--- a/research/traditional_assets/database/data/kenya/kenya_retail_distributors.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_retail_distributors.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.354</v>
+        <v>-0.277</v>
       </c>
       <c r="G2">
-        <v>-0.4635294117647059</v>
+        <v>-0.4670588235294118</v>
       </c>
       <c r="H2">
-        <v>-0.4635294117647059</v>
+        <v>-0.4670588235294118</v>
       </c>
       <c r="I2">
-        <v>-0.5752941176470588</v>
+        <v>-0.3294117647058824</v>
       </c>
       <c r="J2">
-        <v>-0.5752941176470588</v>
+        <v>-0.3294117647058824</v>
       </c>
       <c r="K2">
-        <v>-0.731</v>
+        <v>-0.149</v>
       </c>
       <c r="L2">
-        <v>-0.86</v>
+        <v>-0.1752941176470588</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.545</v>
+        <v>0.528</v>
       </c>
       <c r="V2">
-        <v>0.2994505494505494</v>
+        <v>0.4512820512820513</v>
       </c>
       <c r="W2">
-        <v>-0.8077348066298342</v>
+        <v>-1.087591240875912</v>
       </c>
       <c r="X2">
-        <v>0.08156851087189911</v>
+        <v>0.148929131092203</v>
       </c>
       <c r="Y2">
-        <v>-0.8893033175017333</v>
-      </c>
-      <c r="Z2">
-        <v>1.923076923076923</v>
-      </c>
-      <c r="AA2">
-        <v>-1.106334841628959</v>
+        <v>-1.236520371968115</v>
       </c>
       <c r="AB2">
-        <v>0.07852982380932196</v>
-      </c>
-      <c r="AC2">
-        <v>-1.184864665438281</v>
+        <v>0.1360623151279686</v>
       </c>
       <c r="AD2">
-        <v>0.23</v>
+        <v>0.315</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.23</v>
+        <v>0.315</v>
       </c>
       <c r="AG2">
-        <v>-0.3150000000000001</v>
+        <v>-0.213</v>
       </c>
       <c r="AH2">
-        <v>0.1121951219512195</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="AI2">
-        <v>0.6267029972752044</v>
+        <v>1.064189189189189</v>
       </c>
       <c r="AJ2">
-        <v>-0.2093023255813954</v>
+        <v>-0.2225705329153606</v>
       </c>
       <c r="AK2">
-        <v>1.769662921348314</v>
+        <v>0.9181034482758621</v>
       </c>
       <c r="AL2">
-        <v>0.024</v>
+        <v>0.036</v>
       </c>
       <c r="AM2">
-        <v>-0.037</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="AN2">
-        <v>-0.475206611570248</v>
+        <v>-1.202290076335878</v>
       </c>
       <c r="AO2">
-        <v>-20.375</v>
+        <v>-7.777777777777779</v>
       </c>
       <c r="AP2">
-        <v>0.6508264462809918</v>
+        <v>0.8129770992366413</v>
       </c>
       <c r="AQ2">
-        <v>13.21621621621622</v>
+        <v>40.00000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +707,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.354</v>
+        <v>-0.277</v>
       </c>
       <c r="G3">
-        <v>-0.4635294117647059</v>
+        <v>-0.4670588235294118</v>
       </c>
       <c r="H3">
-        <v>-0.4635294117647059</v>
+        <v>-0.4670588235294118</v>
       </c>
       <c r="I3">
-        <v>-0.5752941176470588</v>
+        <v>-0.3294117647058824</v>
       </c>
       <c r="J3">
-        <v>-0.5752941176470588</v>
+        <v>-0.3294117647058824</v>
       </c>
       <c r="K3">
-        <v>-0.731</v>
+        <v>-0.149</v>
       </c>
       <c r="L3">
-        <v>-0.86</v>
+        <v>-0.1752941176470588</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +749,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.545</v>
+        <v>0.528</v>
       </c>
       <c r="V3">
-        <v>0.2994505494505494</v>
+        <v>0.4512820512820513</v>
       </c>
       <c r="W3">
-        <v>-0.8077348066298342</v>
+        <v>-1.087591240875912</v>
       </c>
       <c r="X3">
-        <v>0.08156851087189911</v>
+        <v>0.148929131092203</v>
       </c>
       <c r="Y3">
-        <v>-0.8893033175017333</v>
-      </c>
-      <c r="Z3">
-        <v>1.923076923076923</v>
-      </c>
-      <c r="AA3">
-        <v>-1.106334841628959</v>
+        <v>-1.236520371968115</v>
       </c>
       <c r="AB3">
-        <v>0.07852982380932196</v>
-      </c>
-      <c r="AC3">
-        <v>-1.184864665438281</v>
+        <v>0.1360623151279686</v>
       </c>
       <c r="AD3">
-        <v>0.23</v>
+        <v>0.315</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.23</v>
+        <v>0.315</v>
       </c>
       <c r="AG3">
-        <v>-0.3150000000000001</v>
+        <v>-0.213</v>
       </c>
       <c r="AH3">
-        <v>0.1121951219512195</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="AI3">
-        <v>0.6267029972752044</v>
+        <v>1.064189189189189</v>
       </c>
       <c r="AJ3">
-        <v>-0.2093023255813954</v>
+        <v>-0.2225705329153606</v>
       </c>
       <c r="AK3">
-        <v>1.769662921348314</v>
+        <v>0.9181034482758621</v>
       </c>
       <c r="AL3">
-        <v>0.024</v>
+        <v>0.036</v>
       </c>
       <c r="AM3">
-        <v>-0.037</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="AN3">
-        <v>-0.475206611570248</v>
+        <v>-1.202290076335878</v>
       </c>
       <c r="AO3">
-        <v>-20.375</v>
+        <v>-7.777777777777779</v>
       </c>
       <c r="AP3">
-        <v>0.6508264462809918</v>
+        <v>0.8129770992366413</v>
       </c>
       <c r="AQ3">
-        <v>13.21621621621622</v>
+        <v>40.00000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kenya/kenya_retail_distributors.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_retail_distributors.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.277</v>
+        <v>-0.269</v>
       </c>
       <c r="G2">
-        <v>-0.4670588235294118</v>
+        <v>-0.09047443913203382</v>
       </c>
       <c r="H2">
-        <v>-0.4670588235294118</v>
+        <v>-0.09047443913203382</v>
       </c>
       <c r="I2">
-        <v>-0.3294117647058824</v>
+        <v>-0.09783008458992276</v>
       </c>
       <c r="J2">
-        <v>-0.3294117647058824</v>
+        <v>-0.07656267489646129</v>
       </c>
       <c r="K2">
-        <v>-0.149</v>
+        <v>-0.389</v>
       </c>
       <c r="L2">
-        <v>-0.1752941176470588</v>
+        <v>-0.1430673041559397</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,64 +630,58 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.528</v>
+        <v>0.074</v>
       </c>
       <c r="V2">
-        <v>0.4512820512820513</v>
-      </c>
-      <c r="W2">
-        <v>-1.087591240875912</v>
+        <v>0.002965931863727455</v>
       </c>
       <c r="X2">
-        <v>0.148929131092203</v>
-      </c>
-      <c r="Y2">
-        <v>-1.236520371968115</v>
+        <v>0.1204165382702482</v>
       </c>
       <c r="AB2">
-        <v>0.1360623151279686</v>
+        <v>0.1204165382702482</v>
       </c>
       <c r="AD2">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.213</v>
+        <v>-0.074</v>
       </c>
       <c r="AH2">
-        <v>0.2121212121212121</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>1.064189189189189</v>
+        <v>-0</v>
       </c>
       <c r="AJ2">
-        <v>-0.2225705329153606</v>
+        <v>-0.002974754783727288</v>
       </c>
       <c r="AK2">
-        <v>0.9181034482758621</v>
+        <v>0.1360294117647059</v>
       </c>
       <c r="AL2">
-        <v>0.036</v>
+        <v>0.021</v>
       </c>
       <c r="AM2">
-        <v>-0.006999999999999999</v>
+        <v>-0.018</v>
       </c>
       <c r="AN2">
-        <v>-1.202290076335878</v>
+        <v>-0</v>
       </c>
       <c r="AO2">
-        <v>-7.777777777777779</v>
+        <v>-12.66666666666667</v>
       </c>
       <c r="AP2">
-        <v>0.8129770992366413</v>
+        <v>0.2835249042145593</v>
       </c>
       <c r="AQ2">
-        <v>40.00000000000001</v>
+        <v>14.77777777777778</v>
       </c>
     </row>
     <row r="3">
@@ -698,115 +692,213 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Nairobi Business Ventures PLC (NASE:NBV)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Retail (Distributors)</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>0.0008583690987124463</v>
+      </c>
+      <c r="H3">
+        <v>0.0008583690987124463</v>
+      </c>
+      <c r="I3">
+        <v>-0.0004291845493562232</v>
+      </c>
+      <c r="J3">
+        <v>-0.0002425825713752566</v>
+      </c>
+      <c r="K3">
+        <v>0.065</v>
+      </c>
+      <c r="L3">
+        <v>0.02789699570815451</v>
+      </c>
+      <c r="M3">
+        <v>-0</v>
+      </c>
+      <c r="N3">
+        <v>-0</v>
+      </c>
+      <c r="O3">
+        <v>-0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>-0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0.1204165382702482</v>
+      </c>
+      <c r="AB3">
+        <v>0.1204165382702482</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Eveready East Africa PLC (NASE:EVRD)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Retail (Distributors)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.277</v>
-      </c>
-      <c r="G3">
-        <v>-0.4670588235294118</v>
-      </c>
-      <c r="H3">
-        <v>-0.4670588235294118</v>
-      </c>
-      <c r="I3">
-        <v>-0.3294117647058824</v>
-      </c>
-      <c r="J3">
-        <v>-0.3294117647058824</v>
-      </c>
-      <c r="K3">
-        <v>-0.149</v>
-      </c>
-      <c r="L3">
-        <v>-0.1752941176470588</v>
-      </c>
-      <c r="M3">
-        <v>-0</v>
-      </c>
-      <c r="N3">
-        <v>-0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>-0</v>
-      </c>
-      <c r="Q3">
-        <v>-0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0.528</v>
-      </c>
-      <c r="V3">
-        <v>0.4512820512820513</v>
-      </c>
-      <c r="W3">
-        <v>-1.087591240875912</v>
-      </c>
-      <c r="X3">
-        <v>0.148929131092203</v>
-      </c>
-      <c r="Y3">
-        <v>-1.236520371968115</v>
-      </c>
-      <c r="AB3">
-        <v>0.1360623151279686</v>
-      </c>
-      <c r="AD3">
-        <v>0.315</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0.315</v>
-      </c>
-      <c r="AG3">
-        <v>-0.213</v>
-      </c>
-      <c r="AH3">
-        <v>0.2121212121212121</v>
-      </c>
-      <c r="AI3">
-        <v>1.064189189189189</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.2225705329153606</v>
-      </c>
-      <c r="AK3">
-        <v>0.9181034482758621</v>
-      </c>
-      <c r="AL3">
-        <v>0.036</v>
-      </c>
-      <c r="AM3">
-        <v>-0.006999999999999999</v>
-      </c>
-      <c r="AN3">
-        <v>-1.202290076335878</v>
-      </c>
-      <c r="AO3">
-        <v>-7.777777777777779</v>
-      </c>
-      <c r="AP3">
-        <v>0.8129770992366413</v>
-      </c>
-      <c r="AQ3">
-        <v>40.00000000000001</v>
+      <c r="D4">
+        <v>-0.269</v>
+      </c>
+      <c r="G4">
+        <v>-0.6375321336760925</v>
+      </c>
+      <c r="H4">
+        <v>-0.6375321336760925</v>
+      </c>
+      <c r="I4">
+        <v>-0.6812339331619537</v>
+      </c>
+      <c r="J4">
+        <v>-0.6812339331619537</v>
+      </c>
+      <c r="K4">
+        <v>-0.454</v>
+      </c>
+      <c r="L4">
+        <v>-1.167095115681234</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.074</v>
+      </c>
+      <c r="V4">
+        <v>0.05103448275862069</v>
+      </c>
+      <c r="W4">
+        <v>23.89473684210526</v>
+      </c>
+      <c r="X4">
+        <v>0.1204165382702482</v>
+      </c>
+      <c r="Y4">
+        <v>23.77432030383502</v>
+      </c>
+      <c r="AB4">
+        <v>0.1204165382702482</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-0.074</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>-0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.05377906976744186</v>
+      </c>
+      <c r="AK4">
+        <v>0.1360294117647059</v>
+      </c>
+      <c r="AL4">
+        <v>0.021</v>
+      </c>
+      <c r="AM4">
+        <v>-0.018</v>
+      </c>
+      <c r="AN4">
+        <v>-0</v>
+      </c>
+      <c r="AO4">
+        <v>-12.61904761904762</v>
+      </c>
+      <c r="AP4">
+        <v>0.2813688212927756</v>
+      </c>
+      <c r="AQ4">
+        <v>14.72222222222222</v>
       </c>
     </row>
   </sheetData>
